--- a/data_mahasiswa.xlsx
+++ b/data_mahasiswa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Documents\aplikasi_buat_CDC\magang\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA507E6-1702-4152-BA87-1A4A028CD10A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7E3EB4D-FB6E-4041-8AC5-C90E7663A6B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{9EB2CA35-51CA-40F6-BC02-A823A6410FF0}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="136">
   <si>
     <t>NIM</t>
   </si>
@@ -133,9 +133,6 @@
   </si>
   <si>
     <t>RIYO RIALDY URDA</t>
-  </si>
-  <si>
-    <t>ADLAN MUAMMAR SHIDDIQ</t>
   </si>
   <si>
     <t>ILHAM NOTOHUSODO</t>
@@ -451,7 +448,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -597,12 +594,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Plus Jakarta Sans"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -961,7 +952,7 @@
     <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -970,9 +961,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1330,7 +1318,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21797419-6635-4282-8C69-CE6E0BF72131}">
-  <dimension ref="A1:C122"/>
+  <dimension ref="A1:C121"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
@@ -1346,7 +1334,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1357,7 +1345,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1368,7 +1356,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1379,7 +1367,7 @@
         <v>4</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1390,7 +1378,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1401,7 +1389,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1412,7 +1400,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1423,7 +1411,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1434,7 +1422,7 @@
         <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1445,7 +1433,7 @@
         <v>10</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1456,7 +1444,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1467,7 +1455,7 @@
         <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1478,7 +1466,7 @@
         <v>13</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1489,7 +1477,7 @@
         <v>14</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1500,7 +1488,7 @@
         <v>15</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1511,7 +1499,7 @@
         <v>16</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1522,7 +1510,7 @@
         <v>17</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1533,7 +1521,7 @@
         <v>18</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1544,7 +1532,7 @@
         <v>19</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1555,7 +1543,7 @@
         <v>20</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1566,7 +1554,7 @@
         <v>21</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1577,7 +1565,7 @@
         <v>22</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1588,7 +1576,7 @@
         <v>23</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1599,7 +1587,7 @@
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1610,7 +1598,7 @@
         <v>25</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1621,7 +1609,7 @@
         <v>26</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1632,7 +1620,7 @@
         <v>27</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1643,7 +1631,7 @@
         <v>28</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1654,7 +1642,7 @@
         <v>29</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1665,7 +1653,7 @@
         <v>30</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1676,7 +1664,7 @@
         <v>31</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1687,34 +1675,34 @@
         <v>32</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2">
-        <v>24120500014</v>
+        <v>24120500018</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2">
-        <v>24120500018</v>
+        <v>24120500022</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2">
-        <v>24120500022</v>
+        <v>24120500023</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>35</v>
@@ -1725,18 +1713,18 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2">
-        <v>24120500023</v>
+        <v>24120500024</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2">
-        <v>24120500024</v>
+        <v>24120500026</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>37</v>
@@ -1747,51 +1735,51 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2">
-        <v>24120500026</v>
+        <v>24120500027</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2">
-        <v>24120500027</v>
+        <v>24120500030</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2">
-        <v>24120500030</v>
+        <v>24120500031</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2">
-        <v>24120500031</v>
+        <v>24120510002</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>102</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2">
-        <v>24120510002</v>
+        <v>24120510003</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>103</v>
@@ -1802,161 +1790,161 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2">
-        <v>24120510003</v>
+        <v>24120510004</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>104</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2">
-        <v>24120510004</v>
+        <v>24120510006</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>105</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="2">
-        <v>24120510006</v>
+        <v>24120510007</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>106</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="2">
-        <v>24120510007</v>
+        <v>24120510012</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>107</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="2">
-        <v>24120510012</v>
+        <v>24120510013</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>108</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="2">
-        <v>24120510013</v>
+        <v>24120510014</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>109</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="2">
-        <v>24120510014</v>
+        <v>24130500001</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="2">
-        <v>24130500001</v>
+        <v>24130500003</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>41</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="2">
-        <v>24130500003</v>
+        <v>24130500004</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="2">
-        <v>24130500004</v>
+        <v>24130500005</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="2">
-        <v>24130500005</v>
+        <v>24130500006</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="2">
-        <v>24130500006</v>
+        <v>24130500007</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>45</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="2">
-        <v>24130500007</v>
+        <v>24130500009</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>46</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="2">
-        <v>24130500009</v>
+        <v>24130500010</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="2">
-        <v>24130500010</v>
+        <v>25110500001</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>48</v>
@@ -1967,7 +1955,7 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="2">
-        <v>25110500001</v>
+        <v>25110500002</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>49</v>
@@ -1978,29 +1966,29 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="2">
-        <v>25110500002</v>
+        <v>25110500003</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="2">
-        <v>25110500003</v>
+        <v>25110500004</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="2">
-        <v>25110500004</v>
+        <v>25110500005</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>52</v>
@@ -2011,18 +1999,18 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="2">
-        <v>25110500005</v>
+        <v>25110500006</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="2">
-        <v>25110500006</v>
+        <v>25110500007</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>54</v>
@@ -2033,62 +2021,62 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="2">
-        <v>25110500007</v>
+        <v>25110500008</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>55</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="2">
-        <v>25110500008</v>
+        <v>25110500009</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>56</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="2">
-        <v>25110500009</v>
+        <v>25110500011</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>57</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="2">
-        <v>25110500011</v>
+        <v>25110500013</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="2">
-        <v>25110500013</v>
+        <v>25110500015</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="2">
-        <v>25110500015</v>
+        <v>25110500016</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>60</v>
@@ -2099,29 +2087,29 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="2">
-        <v>25110500016</v>
+        <v>25110500017</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="2">
-        <v>25110500017</v>
+        <v>25110500018</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>62</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="2">
-        <v>25110500018</v>
+        <v>25110500019</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>63</v>
@@ -2132,18 +2120,18 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="2">
-        <v>25110500019</v>
+        <v>25110500020</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>64</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="2">
-        <v>25110500020</v>
+        <v>25110500021</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>65</v>
@@ -2154,150 +2142,150 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="2">
-        <v>25110500021</v>
+        <v>25110500022</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>66</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="2">
-        <v>25110500022</v>
+        <v>25110500023</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>67</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="2">
-        <v>25110500023</v>
+        <v>25110500024</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="2">
-        <v>25110500024</v>
+        <v>25110500025</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>69</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="2">
-        <v>25110500025</v>
+        <v>25110500026</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="2">
-        <v>25110500026</v>
+        <v>25110500027</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>71</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="2">
-        <v>25110500027</v>
+        <v>25110500029</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>72</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="2">
-        <v>25110500029</v>
+        <v>25110500030</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>73</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" s="2">
-        <v>25110500030</v>
+        <v>25110500032</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>74</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="2">
-        <v>25110500032</v>
+        <v>25110500033</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>75</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="2">
-        <v>25110500033</v>
+        <v>25110500034</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>76</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" s="2">
-        <v>25110500034</v>
+        <v>25120500001</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>77</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" s="2">
-        <v>25120500001</v>
+        <v>25120500002</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>78</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" s="2">
-        <v>25120500002</v>
+        <v>25120500003</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>79</v>
@@ -2308,40 +2296,40 @@
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="2">
-        <v>25120500003</v>
+        <v>25120500004</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>80</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="2">
-        <v>25120500004</v>
+        <v>25120500005</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>81</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" s="2">
-        <v>25120500005</v>
+        <v>25120500006</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>82</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" s="2">
-        <v>25120500006</v>
+        <v>25120500007</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>83</v>
@@ -2352,18 +2340,18 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="2">
-        <v>25120500007</v>
+        <v>25120500008</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>84</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="2">
-        <v>25120500008</v>
+        <v>25120500009</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>85</v>
@@ -2374,40 +2362,40 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="2">
-        <v>25120500009</v>
+        <v>25120500010</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>86</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" s="2">
-        <v>25120500010</v>
+        <v>25120500011</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>87</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" s="2">
-        <v>25120500011</v>
+        <v>25120500012</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>88</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="2">
-        <v>25120500012</v>
+        <v>25120500015</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>89</v>
@@ -2418,84 +2406,84 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="2">
-        <v>25120500015</v>
+        <v>25120500016</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>90</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="2">
-        <v>25120500016</v>
+        <v>25120500017</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>91</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="2">
-        <v>25120500017</v>
+        <v>25120500019</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>92</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" s="2">
-        <v>25120500019</v>
+        <v>25120500020</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>93</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" s="2">
-        <v>25120500020</v>
+        <v>25120500023</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>94</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" s="2">
-        <v>25120500023</v>
+        <v>25120500024</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>95</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" s="2">
-        <v>25120500024</v>
+        <v>25120500025</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>96</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" s="2">
-        <v>25120500025</v>
+        <v>25120500026</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>97</v>
@@ -2506,51 +2494,51 @@
     </row>
     <row r="107" spans="1:3">
       <c r="A107" s="2">
-        <v>25120500026</v>
+        <v>25120500028</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" s="2">
-        <v>25120500028</v>
+        <v>25120500029</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>99</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="2">
-        <v>25120500029</v>
+        <v>25120500032</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>100</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" s="2">
-        <v>25120500032</v>
+        <v>25120510001</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" s="2">
-        <v>25120510001</v>
+        <v>25120510002</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>111</v>
@@ -2561,121 +2549,112 @@
     </row>
     <row r="112" spans="1:3">
       <c r="A112" s="2">
-        <v>25120510002</v>
+        <v>25120510003</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>112</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" s="2">
-        <v>25120510003</v>
+        <v>25120510004</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>113</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" s="2">
-        <v>25120510004</v>
+        <v>25120510005</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>114</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" s="2">
-        <v>25120510005</v>
+        <v>25120510006</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>115</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" s="2">
-        <v>25120510006</v>
+        <v>25120510007</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>116</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="2">
-        <v>25120510007</v>
+        <v>25120510008</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>117</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" s="2">
-        <v>25120510008</v>
+        <v>25120510009</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" s="2">
-        <v>25120510009</v>
+        <v>25120510010</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C119" s="4"/>
+      <c r="C119" s="3" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" s="2">
-        <v>25120510010</v>
+        <v>25120510011</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>120</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" s="2">
-        <v>25120510011</v>
+        <v>25120510012</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>121</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3">
-      <c r="A122" s="2">
-        <v>25120510012</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C122" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
